--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1081,6 +1081,1230 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120104544</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91005</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>502366</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6689377</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120103177</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100080</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>502291</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6689507</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120103137</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101074</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>502278</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6689509</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120102506</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103418</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>502313</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6689509</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120102425</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100080</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>502304</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6689516</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120103115</v>
+      </c>
+      <c r="B11" t="n">
+        <v>103418</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>502278</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6689509</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120104361</v>
+      </c>
+      <c r="B12" t="n">
+        <v>103418</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>502326</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6689308</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120104129</v>
+      </c>
+      <c r="B13" t="n">
+        <v>103418</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>502310</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6689361</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120102514</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91494</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>502324</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6689524</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120102318</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102825</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>502315</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6689529</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120104354</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91494</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>502332</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6689303</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120104289</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101074</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>502332</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6689261</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120104544</v>
+        <v>120102514</v>
       </c>
       <c r="B6" t="n">
-        <v>91005</v>
+        <v>91494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502366</v>
+        <v>502324</v>
       </c>
       <c r="R6" t="n">
-        <v>6689377</v>
+        <v>6689524</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120103177</v>
+        <v>120103115</v>
       </c>
       <c r="B7" t="n">
-        <v>100080</v>
+        <v>103418</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,16 +1201,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502291</v>
+        <v>502278</v>
       </c>
       <c r="R7" t="n">
-        <v>6689507</v>
+        <v>6689509</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120102425</v>
+        <v>120104354</v>
       </c>
       <c r="B10" t="n">
-        <v>100080</v>
+        <v>91494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502304</v>
+        <v>502332</v>
       </c>
       <c r="R10" t="n">
-        <v>6689516</v>
+        <v>6689303</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120103115</v>
+        <v>120102318</v>
       </c>
       <c r="B11" t="n">
-        <v>103418</v>
+        <v>102825</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,16 +1609,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502278</v>
+        <v>502315</v>
       </c>
       <c r="R11" t="n">
-        <v>6689509</v>
+        <v>6689529</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1688,17 +1688,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120104361</v>
+        <v>120102425</v>
       </c>
       <c r="B12" t="n">
-        <v>103418</v>
+        <v>100080</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,16 +1711,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502326</v>
+        <v>502304</v>
       </c>
       <c r="R12" t="n">
-        <v>6689308</v>
+        <v>6689516</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120102514</v>
+        <v>120104544</v>
       </c>
       <c r="B14" t="n">
-        <v>91494</v>
+        <v>91005</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502324</v>
+        <v>502366</v>
       </c>
       <c r="R14" t="n">
-        <v>6689524</v>
+        <v>6689377</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120102318</v>
+        <v>120104289</v>
       </c>
       <c r="B15" t="n">
-        <v>102825</v>
+        <v>101074</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222002</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502315</v>
+        <v>502332</v>
       </c>
       <c r="R15" t="n">
-        <v>6689529</v>
+        <v>6689261</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120104354</v>
+        <v>120104361</v>
       </c>
       <c r="B16" t="n">
-        <v>91494</v>
+        <v>103418</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502332</v>
+        <v>502326</v>
       </c>
       <c r="R16" t="n">
-        <v>6689303</v>
+        <v>6689308</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120104289</v>
+        <v>120103177</v>
       </c>
       <c r="B17" t="n">
-        <v>101074</v>
+        <v>100080</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502332</v>
+        <v>502291</v>
       </c>
       <c r="R17" t="n">
-        <v>6689261</v>
+        <v>6689507</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120102514</v>
+        <v>120104289</v>
       </c>
       <c r="B6" t="n">
-        <v>91494</v>
+        <v>101074</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502324</v>
+        <v>502332</v>
       </c>
       <c r="R6" t="n">
-        <v>6689524</v>
+        <v>6689261</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120103115</v>
+        <v>120102506</v>
       </c>
       <c r="B7" t="n">
         <v>103418</v>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502278</v>
+        <v>502313</v>
       </c>
       <c r="R7" t="n">
         <v>6689509</v>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120103137</v>
+        <v>120104354</v>
       </c>
       <c r="B8" t="n">
-        <v>101074</v>
+        <v>91494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502278</v>
+        <v>502332</v>
       </c>
       <c r="R8" t="n">
-        <v>6689509</v>
+        <v>6689303</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120102506</v>
+        <v>120103137</v>
       </c>
       <c r="B9" t="n">
-        <v>103418</v>
+        <v>101074</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,7 +1429,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502313</v>
+        <v>502278</v>
       </c>
       <c r="R9" t="n">
         <v>6689509</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120104354</v>
+        <v>120104544</v>
       </c>
       <c r="B10" t="n">
-        <v>91494</v>
+        <v>91005</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502332</v>
+        <v>502366</v>
       </c>
       <c r="R10" t="n">
-        <v>6689303</v>
+        <v>6689377</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120102318</v>
+        <v>120104129</v>
       </c>
       <c r="B11" t="n">
-        <v>102825</v>
+        <v>103418</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,16 +1609,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222002</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502315</v>
+        <v>502310</v>
       </c>
       <c r="R11" t="n">
-        <v>6689529</v>
+        <v>6689361</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120102425</v>
+        <v>120103115</v>
       </c>
       <c r="B12" t="n">
-        <v>100080</v>
+        <v>103418</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,16 +1711,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502304</v>
+        <v>502278</v>
       </c>
       <c r="R12" t="n">
-        <v>6689516</v>
+        <v>6689509</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1790,17 +1790,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120104129</v>
+        <v>120102514</v>
       </c>
       <c r="B13" t="n">
-        <v>103418</v>
+        <v>91494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502310</v>
+        <v>502324</v>
       </c>
       <c r="R13" t="n">
-        <v>6689361</v>
+        <v>6689524</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120104544</v>
+        <v>120103177</v>
       </c>
       <c r="B14" t="n">
-        <v>91005</v>
+        <v>100080</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502366</v>
+        <v>502291</v>
       </c>
       <c r="R14" t="n">
-        <v>6689377</v>
+        <v>6689507</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120104289</v>
+        <v>120104361</v>
       </c>
       <c r="B15" t="n">
-        <v>101074</v>
+        <v>103418</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502332</v>
+        <v>502326</v>
       </c>
       <c r="R15" t="n">
-        <v>6689261</v>
+        <v>6689308</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120104361</v>
+        <v>120102318</v>
       </c>
       <c r="B16" t="n">
-        <v>103418</v>
+        <v>102825</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,16 +2119,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502326</v>
+        <v>502315</v>
       </c>
       <c r="R16" t="n">
-        <v>6689308</v>
+        <v>6689529</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120103177</v>
+        <v>120102425</v>
       </c>
       <c r="B17" t="n">
         <v>100080</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502291</v>
+        <v>502304</v>
       </c>
       <c r="R17" t="n">
-        <v>6689507</v>
+        <v>6689516</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120104289</v>
+        <v>120103177</v>
       </c>
       <c r="B6" t="n">
-        <v>101074</v>
+        <v>100080</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502332</v>
+        <v>502291</v>
       </c>
       <c r="R6" t="n">
-        <v>6689261</v>
+        <v>6689507</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120102506</v>
+        <v>120103137</v>
       </c>
       <c r="B7" t="n">
-        <v>103418</v>
+        <v>101074</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502313</v>
+        <v>502278</v>
       </c>
       <c r="R7" t="n">
         <v>6689509</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120104354</v>
+        <v>120102514</v>
       </c>
       <c r="B8" t="n">
         <v>91494</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502332</v>
+        <v>502324</v>
       </c>
       <c r="R8" t="n">
-        <v>6689303</v>
+        <v>6689524</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120103137</v>
+        <v>120102318</v>
       </c>
       <c r="B9" t="n">
-        <v>101074</v>
+        <v>102825</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502278</v>
+        <v>502315</v>
       </c>
       <c r="R9" t="n">
-        <v>6689509</v>
+        <v>6689529</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120104544</v>
+        <v>120104361</v>
       </c>
       <c r="B10" t="n">
-        <v>91005</v>
+        <v>103418</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502366</v>
+        <v>502326</v>
       </c>
       <c r="R10" t="n">
-        <v>6689377</v>
+        <v>6689308</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120104129</v>
+        <v>120103115</v>
       </c>
       <c r="B11" t="n">
         <v>103418</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502310</v>
+        <v>502278</v>
       </c>
       <c r="R11" t="n">
-        <v>6689361</v>
+        <v>6689509</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1688,17 +1688,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120103115</v>
+        <v>120102425</v>
       </c>
       <c r="B12" t="n">
-        <v>103418</v>
+        <v>100080</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,16 +1711,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502278</v>
+        <v>502304</v>
       </c>
       <c r="R12" t="n">
-        <v>6689509</v>
+        <v>6689516</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1790,14 +1790,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120102514</v>
+        <v>120104354</v>
       </c>
       <c r="B13" t="n">
         <v>91494</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502324</v>
+        <v>502332</v>
       </c>
       <c r="R13" t="n">
-        <v>6689524</v>
+        <v>6689303</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120103177</v>
+        <v>120104129</v>
       </c>
       <c r="B14" t="n">
-        <v>100080</v>
+        <v>103418</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,16 +1915,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502291</v>
+        <v>502310</v>
       </c>
       <c r="R14" t="n">
-        <v>6689507</v>
+        <v>6689361</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120104361</v>
+        <v>120104544</v>
       </c>
       <c r="B15" t="n">
-        <v>103418</v>
+        <v>91005</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222412</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502326</v>
+        <v>502366</v>
       </c>
       <c r="R15" t="n">
-        <v>6689308</v>
+        <v>6689377</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120102318</v>
+        <v>120102506</v>
       </c>
       <c r="B16" t="n">
-        <v>102825</v>
+        <v>103418</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,16 +2119,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222002</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502315</v>
+        <v>502313</v>
       </c>
       <c r="R16" t="n">
-        <v>6689529</v>
+        <v>6689509</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120102425</v>
+        <v>120104289</v>
       </c>
       <c r="B17" t="n">
-        <v>100080</v>
+        <v>101074</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502304</v>
+        <v>502332</v>
       </c>
       <c r="R17" t="n">
-        <v>6689516</v>
+        <v>6689261</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120104544</v>
+        <v>120102506</v>
       </c>
       <c r="B15" t="n">
-        <v>91005</v>
+        <v>103418</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>222412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502366</v>
+        <v>502313</v>
       </c>
       <c r="R15" t="n">
-        <v>6689377</v>
+        <v>6689509</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120102506</v>
+        <v>120104544</v>
       </c>
       <c r="B16" t="n">
-        <v>103418</v>
+        <v>91005</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502313</v>
+        <v>502366</v>
       </c>
       <c r="R16" t="n">
-        <v>6689509</v>
+        <v>6689377</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120102506</v>
+        <v>120104544</v>
       </c>
       <c r="B15" t="n">
-        <v>103418</v>
+        <v>91005</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222412</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502313</v>
+        <v>502366</v>
       </c>
       <c r="R15" t="n">
-        <v>6689509</v>
+        <v>6689377</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120104544</v>
+        <v>120102506</v>
       </c>
       <c r="B16" t="n">
-        <v>91005</v>
+        <v>103418</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502366</v>
+        <v>502313</v>
       </c>
       <c r="R16" t="n">
-        <v>6689377</v>
+        <v>6689509</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120103177</v>
+        <v>120103115</v>
       </c>
       <c r="B6" t="n">
-        <v>100080</v>
+        <v>103441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502291</v>
+        <v>502278</v>
       </c>
       <c r="R6" t="n">
-        <v>6689507</v>
+        <v>6689509</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120103137</v>
+        <v>120104361</v>
       </c>
       <c r="B7" t="n">
-        <v>101074</v>
+        <v>103441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502278</v>
+        <v>502326</v>
       </c>
       <c r="R7" t="n">
-        <v>6689509</v>
+        <v>6689308</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120102514</v>
+        <v>120104129</v>
       </c>
       <c r="B8" t="n">
-        <v>91494</v>
+        <v>103441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502324</v>
+        <v>502310</v>
       </c>
       <c r="R8" t="n">
-        <v>6689524</v>
+        <v>6689361</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120102318</v>
+        <v>120104289</v>
       </c>
       <c r="B9" t="n">
-        <v>102825</v>
+        <v>101097</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222002</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502315</v>
+        <v>502332</v>
       </c>
       <c r="R9" t="n">
-        <v>6689529</v>
+        <v>6689261</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120104361</v>
+        <v>120104544</v>
       </c>
       <c r="B10" t="n">
-        <v>103418</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222412</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502326</v>
+        <v>502366</v>
       </c>
       <c r="R10" t="n">
-        <v>6689308</v>
+        <v>6689377</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120103115</v>
+        <v>120102506</v>
       </c>
       <c r="B11" t="n">
-        <v>103418</v>
+        <v>103441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502278</v>
+        <v>502313</v>
       </c>
       <c r="R11" t="n">
         <v>6689509</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1698,7 +1698,7 @@
         <v>120102425</v>
       </c>
       <c r="B12" t="n">
-        <v>100080</v>
+        <v>100103</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>120104354</v>
       </c>
       <c r="B13" t="n">
-        <v>91494</v>
+        <v>91512</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120104129</v>
+        <v>120102514</v>
       </c>
       <c r="B14" t="n">
-        <v>103418</v>
+        <v>91512</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502310</v>
+        <v>502324</v>
       </c>
       <c r="R14" t="n">
-        <v>6689361</v>
+        <v>6689524</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120104544</v>
+        <v>120103177</v>
       </c>
       <c r="B15" t="n">
-        <v>91005</v>
+        <v>100103</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>222771</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502366</v>
+        <v>502291</v>
       </c>
       <c r="R15" t="n">
-        <v>6689377</v>
+        <v>6689507</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120102506</v>
+        <v>120102318</v>
       </c>
       <c r="B16" t="n">
-        <v>103418</v>
+        <v>102848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,16 +2119,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502313</v>
+        <v>502315</v>
       </c>
       <c r="R16" t="n">
-        <v>6689509</v>
+        <v>6689529</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120104289</v>
+        <v>120103137</v>
       </c>
       <c r="B17" t="n">
-        <v>101074</v>
+        <v>101097</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502332</v>
+        <v>502278</v>
       </c>
       <c r="R17" t="n">
-        <v>6689261</v>
+        <v>6689509</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120103115</v>
+        <v>120104129</v>
       </c>
       <c r="B6" t="n">
         <v>103441</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502278</v>
+        <v>502310</v>
       </c>
       <c r="R6" t="n">
-        <v>6689509</v>
+        <v>6689361</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1178,14 +1178,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120104361</v>
+        <v>120102506</v>
       </c>
       <c r="B7" t="n">
         <v>103441</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502326</v>
+        <v>502313</v>
       </c>
       <c r="R7" t="n">
-        <v>6689308</v>
+        <v>6689509</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120104129</v>
+        <v>120104361</v>
       </c>
       <c r="B8" t="n">
         <v>103441</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502310</v>
+        <v>502326</v>
       </c>
       <c r="R8" t="n">
-        <v>6689361</v>
+        <v>6689308</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120104289</v>
+        <v>120103137</v>
       </c>
       <c r="B9" t="n">
         <v>101097</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502332</v>
+        <v>502278</v>
       </c>
       <c r="R9" t="n">
-        <v>6689261</v>
+        <v>6689509</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120104544</v>
+        <v>120104354</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>91512</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502366</v>
+        <v>502332</v>
       </c>
       <c r="R10" t="n">
-        <v>6689377</v>
+        <v>6689303</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120102506</v>
+        <v>120103115</v>
       </c>
       <c r="B11" t="n">
         <v>103441</v>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502313</v>
+        <v>502278</v>
       </c>
       <c r="R11" t="n">
         <v>6689509</v>
@@ -1688,17 +1688,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120102425</v>
+        <v>120104544</v>
       </c>
       <c r="B12" t="n">
-        <v>100103</v>
+        <v>91023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502304</v>
+        <v>502366</v>
       </c>
       <c r="R12" t="n">
-        <v>6689516</v>
+        <v>6689377</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120104354</v>
+        <v>120104289</v>
       </c>
       <c r="B13" t="n">
-        <v>91512</v>
+        <v>101097</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1840,7 +1840,7 @@
         <v>502332</v>
       </c>
       <c r="R13" t="n">
-        <v>6689303</v>
+        <v>6689261</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120102514</v>
+        <v>120102425</v>
       </c>
       <c r="B14" t="n">
-        <v>91512</v>
+        <v>100103</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502324</v>
+        <v>502304</v>
       </c>
       <c r="R14" t="n">
-        <v>6689524</v>
+        <v>6689516</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120103177</v>
+        <v>120102318</v>
       </c>
       <c r="B15" t="n">
-        <v>100103</v>
+        <v>102848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,16 +2017,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222771</v>
+        <v>222002</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502291</v>
+        <v>502315</v>
       </c>
       <c r="R15" t="n">
-        <v>6689507</v>
+        <v>6689529</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120102318</v>
+        <v>120102514</v>
       </c>
       <c r="B16" t="n">
-        <v>102848</v>
+        <v>91512</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502315</v>
+        <v>502324</v>
       </c>
       <c r="R16" t="n">
-        <v>6689529</v>
+        <v>6689524</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120103137</v>
+        <v>120103177</v>
       </c>
       <c r="B17" t="n">
-        <v>101097</v>
+        <v>100103</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502278</v>
+        <v>502291</v>
       </c>
       <c r="R17" t="n">
-        <v>6689509</v>
+        <v>6689507</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120104544</v>
+        <v>120104289</v>
       </c>
       <c r="B12" t="n">
-        <v>91023</v>
+        <v>101097</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>221235</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502366</v>
+        <v>502332</v>
       </c>
       <c r="R12" t="n">
-        <v>6689377</v>
+        <v>6689261</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120104289</v>
+        <v>120104544</v>
       </c>
       <c r="B13" t="n">
-        <v>101097</v>
+        <v>91023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221235</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502332</v>
+        <v>502366</v>
       </c>
       <c r="R13" t="n">
-        <v>6689261</v>
+        <v>6689377</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120104129</v>
+        <v>120104354</v>
       </c>
       <c r="B6" t="n">
-        <v>103441</v>
+        <v>91512</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502310</v>
+        <v>502332</v>
       </c>
       <c r="R6" t="n">
-        <v>6689361</v>
+        <v>6689303</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120102506</v>
+        <v>120104544</v>
       </c>
       <c r="B7" t="n">
-        <v>103441</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502313</v>
+        <v>502366</v>
       </c>
       <c r="R7" t="n">
-        <v>6689509</v>
+        <v>6689377</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120103137</v>
+        <v>120102318</v>
       </c>
       <c r="B9" t="n">
-        <v>101097</v>
+        <v>102848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502278</v>
+        <v>502315</v>
       </c>
       <c r="R9" t="n">
-        <v>6689509</v>
+        <v>6689529</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120104354</v>
+        <v>120102425</v>
       </c>
       <c r="B10" t="n">
-        <v>91512</v>
+        <v>100103</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502332</v>
+        <v>502304</v>
       </c>
       <c r="R10" t="n">
-        <v>6689303</v>
+        <v>6689516</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120103115</v>
+        <v>120102514</v>
       </c>
       <c r="B11" t="n">
-        <v>103441</v>
+        <v>91512</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502278</v>
+        <v>502324</v>
       </c>
       <c r="R11" t="n">
-        <v>6689509</v>
+        <v>6689524</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1688,14 +1688,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120104289</v>
+        <v>120103137</v>
       </c>
       <c r="B12" t="n">
         <v>101097</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502332</v>
+        <v>502278</v>
       </c>
       <c r="R12" t="n">
-        <v>6689261</v>
+        <v>6689509</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120104544</v>
+        <v>120103115</v>
       </c>
       <c r="B13" t="n">
-        <v>91023</v>
+        <v>103441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502366</v>
+        <v>502278</v>
       </c>
       <c r="R13" t="n">
-        <v>6689377</v>
+        <v>6689509</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1892,17 +1892,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120102425</v>
+        <v>120104129</v>
       </c>
       <c r="B14" t="n">
-        <v>100103</v>
+        <v>103441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,16 +1915,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502304</v>
+        <v>502310</v>
       </c>
       <c r="R14" t="n">
-        <v>6689516</v>
+        <v>6689361</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120102318</v>
+        <v>120102506</v>
       </c>
       <c r="B15" t="n">
-        <v>102848</v>
+        <v>103441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,16 +2017,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222002</v>
+        <v>222412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502315</v>
+        <v>502313</v>
       </c>
       <c r="R15" t="n">
-        <v>6689529</v>
+        <v>6689509</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120102514</v>
+        <v>120103177</v>
       </c>
       <c r="B16" t="n">
-        <v>91512</v>
+        <v>100103</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502324</v>
+        <v>502291</v>
       </c>
       <c r="R16" t="n">
-        <v>6689524</v>
+        <v>6689507</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120103177</v>
+        <v>120104289</v>
       </c>
       <c r="B17" t="n">
-        <v>100103</v>
+        <v>101097</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502291</v>
+        <v>502332</v>
       </c>
       <c r="R17" t="n">
-        <v>6689507</v>
+        <v>6689261</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120104354</v>
+        <v>120102514</v>
       </c>
       <c r="B6" t="n">
         <v>91512</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502332</v>
+        <v>502324</v>
       </c>
       <c r="R6" t="n">
-        <v>6689303</v>
+        <v>6689524</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120104544</v>
+        <v>120104129</v>
       </c>
       <c r="B7" t="n">
-        <v>91023</v>
+        <v>103441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502366</v>
+        <v>502310</v>
       </c>
       <c r="R7" t="n">
-        <v>6689377</v>
+        <v>6689361</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120104361</v>
+        <v>120104354</v>
       </c>
       <c r="B8" t="n">
-        <v>103441</v>
+        <v>91512</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502326</v>
+        <v>502332</v>
       </c>
       <c r="R8" t="n">
-        <v>6689308</v>
+        <v>6689303</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120102318</v>
+        <v>120103177</v>
       </c>
       <c r="B9" t="n">
-        <v>102848</v>
+        <v>100103</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,16 +1405,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222002</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502315</v>
+        <v>502291</v>
       </c>
       <c r="R9" t="n">
-        <v>6689529</v>
+        <v>6689507</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120102425</v>
+        <v>120104289</v>
       </c>
       <c r="B10" t="n">
-        <v>100103</v>
+        <v>101097</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502304</v>
+        <v>502332</v>
       </c>
       <c r="R10" t="n">
-        <v>6689516</v>
+        <v>6689261</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120102514</v>
+        <v>120103115</v>
       </c>
       <c r="B11" t="n">
-        <v>91512</v>
+        <v>103441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502324</v>
+        <v>502278</v>
       </c>
       <c r="R11" t="n">
-        <v>6689524</v>
+        <v>6689509</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1688,17 +1688,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120103137</v>
+        <v>120102506</v>
       </c>
       <c r="B12" t="n">
-        <v>101097</v>
+        <v>103441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502278</v>
+        <v>502313</v>
       </c>
       <c r="R12" t="n">
         <v>6689509</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120103115</v>
+        <v>120104361</v>
       </c>
       <c r="B13" t="n">
         <v>103441</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502278</v>
+        <v>502326</v>
       </c>
       <c r="R13" t="n">
-        <v>6689509</v>
+        <v>6689308</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1892,17 +1892,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120104129</v>
+        <v>120102318</v>
       </c>
       <c r="B14" t="n">
-        <v>103441</v>
+        <v>102848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,16 +1915,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502310</v>
+        <v>502315</v>
       </c>
       <c r="R14" t="n">
-        <v>6689361</v>
+        <v>6689529</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120102506</v>
+        <v>120103137</v>
       </c>
       <c r="B15" t="n">
-        <v>103441</v>
+        <v>101097</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502313</v>
+        <v>502278</v>
       </c>
       <c r="R15" t="n">
         <v>6689509</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120103177</v>
+        <v>120104544</v>
       </c>
       <c r="B16" t="n">
-        <v>100103</v>
+        <v>91023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502291</v>
+        <v>502366</v>
       </c>
       <c r="R16" t="n">
-        <v>6689507</v>
+        <v>6689377</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120104289</v>
+        <v>120102425</v>
       </c>
       <c r="B17" t="n">
-        <v>101097</v>
+        <v>100103</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502332</v>
+        <v>502304</v>
       </c>
       <c r="R17" t="n">
-        <v>6689261</v>
+        <v>6689516</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120102514</v>
+        <v>120104129</v>
       </c>
       <c r="B6" t="n">
-        <v>91512</v>
+        <v>103441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502324</v>
+        <v>502310</v>
       </c>
       <c r="R6" t="n">
-        <v>6689524</v>
+        <v>6689361</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120104129</v>
+        <v>120104544</v>
       </c>
       <c r="B7" t="n">
-        <v>103441</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502310</v>
+        <v>502366</v>
       </c>
       <c r="R7" t="n">
-        <v>6689361</v>
+        <v>6689377</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120104354</v>
+        <v>120104289</v>
       </c>
       <c r="B8" t="n">
-        <v>91512</v>
+        <v>101097</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
         <v>502332</v>
       </c>
       <c r="R8" t="n">
-        <v>6689303</v>
+        <v>6689261</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120104289</v>
+        <v>120103137</v>
       </c>
       <c r="B10" t="n">
         <v>101097</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502332</v>
+        <v>502278</v>
       </c>
       <c r="R10" t="n">
-        <v>6689261</v>
+        <v>6689509</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120103115</v>
+        <v>120102514</v>
       </c>
       <c r="B11" t="n">
-        <v>103441</v>
+        <v>91512</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502278</v>
+        <v>502324</v>
       </c>
       <c r="R11" t="n">
-        <v>6689509</v>
+        <v>6689524</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1688,14 +1688,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120102506</v>
+        <v>120103115</v>
       </c>
       <c r="B12" t="n">
         <v>103441</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502313</v>
+        <v>502278</v>
       </c>
       <c r="R12" t="n">
         <v>6689509</v>
@@ -1790,17 +1790,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120104361</v>
+        <v>120102318</v>
       </c>
       <c r="B13" t="n">
-        <v>103441</v>
+        <v>102848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,16 +1813,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502326</v>
+        <v>502315</v>
       </c>
       <c r="R13" t="n">
-        <v>6689308</v>
+        <v>6689529</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120102318</v>
+        <v>120104354</v>
       </c>
       <c r="B14" t="n">
-        <v>102848</v>
+        <v>91512</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502315</v>
+        <v>502332</v>
       </c>
       <c r="R14" t="n">
-        <v>6689529</v>
+        <v>6689303</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120103137</v>
+        <v>120102506</v>
       </c>
       <c r="B15" t="n">
-        <v>101097</v>
+        <v>103441</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502278</v>
+        <v>502313</v>
       </c>
       <c r="R15" t="n">
         <v>6689509</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120104544</v>
+        <v>120104361</v>
       </c>
       <c r="B16" t="n">
-        <v>91023</v>
+        <v>103441</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>222412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502366</v>
+        <v>502326</v>
       </c>
       <c r="R16" t="n">
-        <v>6689377</v>
+        <v>6689308</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120104544</v>
+        <v>120104289</v>
       </c>
       <c r="B7" t="n">
-        <v>91023</v>
+        <v>101097</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>221235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502366</v>
+        <v>502332</v>
       </c>
       <c r="R7" t="n">
-        <v>6689377</v>
+        <v>6689261</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120104289</v>
+        <v>120104544</v>
       </c>
       <c r="B8" t="n">
-        <v>101097</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502332</v>
+        <v>502366</v>
       </c>
       <c r="R8" t="n">
-        <v>6689261</v>
+        <v>6689377</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120104129</v>
+        <v>120102425</v>
       </c>
       <c r="B6" t="n">
-        <v>103441</v>
+        <v>100103</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502310</v>
+        <v>502304</v>
       </c>
       <c r="R6" t="n">
-        <v>6689361</v>
+        <v>6689516</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120104289</v>
+        <v>120102318</v>
       </c>
       <c r="B7" t="n">
-        <v>101097</v>
+        <v>102848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>222002</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502332</v>
+        <v>502315</v>
       </c>
       <c r="R7" t="n">
-        <v>6689261</v>
+        <v>6689529</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120104544</v>
+        <v>120103115</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>103441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502366</v>
+        <v>502278</v>
       </c>
       <c r="R8" t="n">
-        <v>6689377</v>
+        <v>6689509</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1382,17 +1382,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120103177</v>
+        <v>120104361</v>
       </c>
       <c r="B9" t="n">
-        <v>100103</v>
+        <v>103441</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,16 +1405,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502291</v>
+        <v>502326</v>
       </c>
       <c r="R9" t="n">
-        <v>6689507</v>
+        <v>6689308</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120103137</v>
+        <v>120103177</v>
       </c>
       <c r="B10" t="n">
-        <v>101097</v>
+        <v>100103</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502278</v>
+        <v>502291</v>
       </c>
       <c r="R10" t="n">
-        <v>6689509</v>
+        <v>6689507</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120102514</v>
+        <v>120104129</v>
       </c>
       <c r="B11" t="n">
-        <v>91512</v>
+        <v>103441</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502324</v>
+        <v>502310</v>
       </c>
       <c r="R11" t="n">
-        <v>6689524</v>
+        <v>6689361</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120103115</v>
+        <v>120104544</v>
       </c>
       <c r="B12" t="n">
-        <v>103441</v>
+        <v>91023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502278</v>
+        <v>502366</v>
       </c>
       <c r="R12" t="n">
-        <v>6689509</v>
+        <v>6689377</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1790,17 +1790,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120102318</v>
+        <v>120102514</v>
       </c>
       <c r="B13" t="n">
-        <v>102848</v>
+        <v>91512</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222002</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502315</v>
+        <v>502324</v>
       </c>
       <c r="R13" t="n">
-        <v>6689529</v>
+        <v>6689524</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120104354</v>
+        <v>120103137</v>
       </c>
       <c r="B14" t="n">
-        <v>91512</v>
+        <v>101097</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502332</v>
+        <v>502278</v>
       </c>
       <c r="R14" t="n">
-        <v>6689303</v>
+        <v>6689509</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120102506</v>
+        <v>120104354</v>
       </c>
       <c r="B15" t="n">
-        <v>103441</v>
+        <v>91512</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502313</v>
+        <v>502332</v>
       </c>
       <c r="R15" t="n">
-        <v>6689509</v>
+        <v>6689303</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120104361</v>
+        <v>120104289</v>
       </c>
       <c r="B16" t="n">
-        <v>103441</v>
+        <v>101097</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502326</v>
+        <v>502332</v>
       </c>
       <c r="R16" t="n">
-        <v>6689308</v>
+        <v>6689261</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120102425</v>
+        <v>120102506</v>
       </c>
       <c r="B17" t="n">
-        <v>100103</v>
+        <v>103441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,16 +2221,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502304</v>
+        <v>502313</v>
       </c>
       <c r="R17" t="n">
-        <v>6689516</v>
+        <v>6689509</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120102425</v>
+        <v>120104129</v>
       </c>
       <c r="B6" t="n">
-        <v>100103</v>
+        <v>103441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502304</v>
+        <v>502310</v>
       </c>
       <c r="R6" t="n">
-        <v>6689516</v>
+        <v>6689361</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120102318</v>
+        <v>120103177</v>
       </c>
       <c r="B7" t="n">
-        <v>102848</v>
+        <v>100103</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,16 +1201,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222002</v>
+        <v>222771</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502315</v>
+        <v>502291</v>
       </c>
       <c r="R7" t="n">
-        <v>6689529</v>
+        <v>6689507</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120103115</v>
+        <v>120103137</v>
       </c>
       <c r="B8" t="n">
-        <v>103441</v>
+        <v>101097</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,17 +1382,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120104361</v>
+        <v>120102318</v>
       </c>
       <c r="B9" t="n">
-        <v>103441</v>
+        <v>102848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,16 +1405,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>222002</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502326</v>
+        <v>502315</v>
       </c>
       <c r="R9" t="n">
-        <v>6689308</v>
+        <v>6689529</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120103177</v>
+        <v>120102506</v>
       </c>
       <c r="B10" t="n">
-        <v>100103</v>
+        <v>103441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,16 +1507,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502291</v>
+        <v>502313</v>
       </c>
       <c r="R10" t="n">
-        <v>6689507</v>
+        <v>6689509</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120104129</v>
+        <v>120102514</v>
       </c>
       <c r="B11" t="n">
-        <v>103441</v>
+        <v>91512</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502310</v>
+        <v>502324</v>
       </c>
       <c r="R11" t="n">
-        <v>6689361</v>
+        <v>6689524</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120102514</v>
+        <v>120103115</v>
       </c>
       <c r="B13" t="n">
-        <v>91512</v>
+        <v>103441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502324</v>
+        <v>502278</v>
       </c>
       <c r="R13" t="n">
-        <v>6689524</v>
+        <v>6689509</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1892,17 +1892,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120103137</v>
+        <v>120102425</v>
       </c>
       <c r="B14" t="n">
-        <v>101097</v>
+        <v>100103</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502278</v>
+        <v>502304</v>
       </c>
       <c r="R14" t="n">
-        <v>6689509</v>
+        <v>6689516</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2205,7 +2205,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120102506</v>
+        <v>120104361</v>
       </c>
       <c r="B17" t="n">
         <v>103441</v>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502313</v>
+        <v>502326</v>
       </c>
       <c r="R17" t="n">
-        <v>6689509</v>
+        <v>6689308</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120104544</v>
+        <v>120103115</v>
       </c>
       <c r="B12" t="n">
-        <v>91023</v>
+        <v>103441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502366</v>
+        <v>502278</v>
       </c>
       <c r="R12" t="n">
-        <v>6689377</v>
+        <v>6689509</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1790,17 +1790,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120103115</v>
+        <v>120104544</v>
       </c>
       <c r="B13" t="n">
-        <v>103441</v>
+        <v>91023</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502278</v>
+        <v>502366</v>
       </c>
       <c r="R13" t="n">
-        <v>6689509</v>
+        <v>6689377</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 31749-2024 artfynd.xlsx
+++ b/artfynd/A 31749-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119337848</v>
+        <v>120104544</v>
       </c>
       <c r="B2" t="n">
-        <v>101074</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502381</v>
+        <v>502366</v>
       </c>
       <c r="R2" t="n">
-        <v>6689576</v>
+        <v>6689377</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119336496</v>
+        <v>119336246</v>
       </c>
       <c r="B3" t="n">
-        <v>91494</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>4740</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502303</v>
+        <v>502394</v>
       </c>
       <c r="R3" t="n">
-        <v>6689462</v>
+        <v>6689369</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119336168</v>
+        <v>119336496</v>
       </c>
       <c r="B4" t="n">
-        <v>100171</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502436</v>
+        <v>502303</v>
       </c>
       <c r="R4" t="n">
-        <v>6689366</v>
+        <v>6689462</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119336246</v>
+        <v>120102514</v>
       </c>
       <c r="B5" t="n">
-        <v>91456</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4740</v>
+        <v>4769</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502394</v>
+        <v>502324</v>
       </c>
       <c r="R5" t="n">
-        <v>6689369</v>
+        <v>6689524</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,22 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120102514</v>
+        <v>120104354</v>
       </c>
       <c r="B6" t="n">
-        <v>91512</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,7 +1088,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502324</v>
+        <v>502332</v>
       </c>
       <c r="R6" t="n">
-        <v>6689524</v>
+        <v>6689303</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120104129</v>
+        <v>119337848</v>
       </c>
       <c r="B7" t="n">
-        <v>103441</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502310</v>
+        <v>502381</v>
       </c>
       <c r="R7" t="n">
-        <v>6689361</v>
+        <v>6689576</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1255,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,44 +1250,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120104544</v>
+        <v>120103137</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502366</v>
+        <v>502278</v>
       </c>
       <c r="R8" t="n">
-        <v>6689377</v>
+        <v>6689509</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120103115</v>
+        <v>120104159</v>
       </c>
       <c r="B9" t="n">
-        <v>103441</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502278</v>
+        <v>502292</v>
       </c>
       <c r="R9" t="n">
-        <v>6689509</v>
+        <v>6689341</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1484,7 +1444,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patric Engfeldt</t>
+          <t>Patric Engfeldt, Anders Janols</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1494,16 +1454,11 @@
         <v>120104289</v>
       </c>
       <c r="B10" t="n">
-        <v>101097</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1596,12 +1551,7 @@
         <v>120102318</v>
       </c>
       <c r="B11" t="n">
-        <v>102848</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,12 +1648,7 @@
         <v>120102506</v>
       </c>
       <c r="B12" t="n">
-        <v>103441</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120103177</v>
+        <v>120103115</v>
       </c>
       <c r="B13" t="n">
-        <v>100103</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,16 +1753,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1837,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502291</v>
+        <v>502278</v>
       </c>
       <c r="R13" t="n">
-        <v>6689507</v>
+        <v>6689509</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1892,22 +1832,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120104354</v>
+        <v>120104129</v>
       </c>
       <c r="B14" t="n">
-        <v>91512</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502332</v>
+        <v>502310</v>
       </c>
       <c r="R14" t="n">
-        <v>6689303</v>
+        <v>6689361</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2001,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120103137</v>
+        <v>120104361</v>
       </c>
       <c r="B15" t="n">
-        <v>101097</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502278</v>
+        <v>502326</v>
       </c>
       <c r="R15" t="n">
-        <v>6689509</v>
+        <v>6689308</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2103,15 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120102425</v>
+        <v>119336168</v>
       </c>
       <c r="B16" t="n">
-        <v>100103</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2119,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502304</v>
+        <v>502436</v>
       </c>
       <c r="R16" t="n">
-        <v>6689516</v>
+        <v>6689366</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2173,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2198,22 +2123,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Anders Janols</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120104361</v>
+        <v>120102425</v>
       </c>
       <c r="B17" t="n">
-        <v>103441</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2221,16 +2141,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2245,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502326</v>
+        <v>502304</v>
       </c>
       <c r="R17" t="n">
-        <v>6689308</v>
+        <v>6689516</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2304,6 +2224,103 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120103177</v>
+      </c>
+      <c r="B18" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lindbastmora, Lindbastmora, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>502291</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6689507</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt, Anders Janols</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
